--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="N10" t="n">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="M12" t="n">
         <v>3.75</v>
       </c>
       <c r="N12" t="n">
-        <v>5.36</v>
+        <v>5.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.04</v>
+        <v>3.68</v>
       </c>
       <c r="M9" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="M11" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI14"/>
+  <dimension ref="A1:AI16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46037.71875</v>
+        <v>46037.70833333334</v>
       </c>
     </row>
     <row r="13">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46037.79166666666</v>
+        <v>46037.70833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2046,116 +2046,354 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>FC Vizela</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Paços de Ferreira</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="n">
+        <v>46037.71875</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Tivoli Gardens</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n">
+        <v>46037.79166666666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Chapelton</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="3" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="n">
         <v>46037.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -1501,40 +1501,40 @@
         <v>2.04</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AA9" t="n">
         <v>2.25</v>
@@ -1543,22 +1543,22 @@
         <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46037.60416666666</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="M9" t="n">
         <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
         <v>4</v>
@@ -1507,22 +1507,22 @@
         <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
         <v>2.62</v>
       </c>
       <c r="T9" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
         <v>1.31</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
@@ -1546,13 +1546,13 @@
         <v>4.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
         <v>1.92</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AG9" t="n">
         <v>1.28</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.84</v>
+        <v>2.97</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46037.69791666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2096,40 +2096,40 @@
         <v>5.3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.92</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA14" t="n">
         <v>1.95</v>
@@ -2138,22 +2138,22 @@
         <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46037.71875</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -1492,34 +1492,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="M9" t="n">
         <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="O9" t="n">
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
         <v>2.62</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T9" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="U9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
         <v>8.800000000000001</v>
@@ -1528,13 +1528,13 @@
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
         <v>2.25</v>
@@ -1543,16 +1543,16 @@
         <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
         <v>1.92</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
         <v>1.28</v>
@@ -1620,40 +1620,40 @@
         <v>3.03</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AA10" t="n">
         <v>2.1</v>
@@ -1662,22 +1662,22 @@
         <v>1.75</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46037.6875</v>
@@ -1730,19 +1730,19 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.97</v>
+        <v>2.84</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
         <v>3.19</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
         <v>2.94</v>
@@ -1751,13 +1751,13 @@
         <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="T11" t="n">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
         <v>7.5</v>
@@ -1775,28 +1775,28 @@
         <v>3.35</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AD11" t="n">
         <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46037.69791666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2096,19 +2096,19 @@
         <v>5.3</v>
       </c>
       <c r="O14" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="P14" t="n">
         <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.92</v>
+        <v>4.84</v>
       </c>
       <c r="R14" t="n">
         <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.98</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
         <v>2.85</v>
@@ -2138,19 +2138,19 @@
         <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.28</v>
+        <v>2.97</v>
       </c>
       <c r="AD14" t="n">
         <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
         <v>2.25</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI16"/>
+  <dimension ref="A1:AI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46037.42013888889</v>
+        <v>46037.41666666666</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46037.47916666666</v>
+        <v>46037.41666666666</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46037.52083333334</v>
+        <v>46037.42013888889</v>
       </c>
     </row>
     <row r="7">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46037.53125</v>
+        <v>46037.47916666666</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46037.5625</v>
+        <v>46037.52083333334</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46037.60416666666</v>
+        <v>46037.53125</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46037.6875</v>
+        <v>46037.5625</v>
       </c>
     </row>
     <row r="11">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.84</v>
+        <v>3.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="O11" t="n">
-        <v>3.19</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="T11" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.38</v>
       </c>
-      <c r="V11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z11" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.44</v>
+        <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46037.69791666666</v>
+        <v>46037.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,76 +1849,76 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>46037.70833333334</v>
+        <v>46037.6875</v>
       </c>
     </row>
     <row r="13">
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,76 +1968,76 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>46037.70833333334</v>
+        <v>46037.69791666666</v>
       </c>
     </row>
     <row r="14">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46037.71875</v>
+        <v>46037.70833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46037.79166666666</v>
+        <v>46037.70833333334</v>
       </c>
     </row>
     <row r="16">
@@ -2284,116 +2284,354 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Portugal LigaPro</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FC Vizela</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Paços de Ferreira</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI16" s="3" t="n">
+        <v>46037.71875</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Tivoli Gardens</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Montego Bay United</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>46037.79166666666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Chapelton</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Arnett Gardens</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="3" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3" t="n">
         <v>46037.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -1739,13 +1739,13 @@
         <v>2.04</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>4.51</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="R11" t="n">
         <v>1.47</v>
@@ -1769,7 +1769,7 @@
         <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
         <v>3</v>
@@ -1781,7 +1781,7 @@
         <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
         <v>1.2</v>
@@ -1858,22 +1858,22 @@
         <v>3.03</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P12" t="n">
         <v>1.96</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="R12" t="n">
         <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.71</v>
+        <v>2.57</v>
       </c>
       <c r="T12" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="U12" t="n">
         <v>1.34</v>
@@ -1885,13 +1885,13 @@
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
         <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.03</v>
+        <v>2.84</v>
       </c>
       <c r="AA12" t="n">
         <v>2.1</v>
@@ -1900,10 +1900,10 @@
         <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
         <v>1.86</v>
@@ -1912,10 +1912,10 @@
         <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46037.6875</v>
@@ -1989,28 +1989,28 @@
         <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="T13" t="n">
-        <v>2.85</v>
+        <v>3.06</v>
       </c>
       <c r="U13" t="n">
         <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.35</v>
+        <v>3.42</v>
       </c>
       <c r="AA13" t="n">
         <v>2.05</v>
@@ -2019,10 +2019,10 @@
         <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
         <v>1.8</v>
@@ -2034,7 +2034,7 @@
         <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46037.69791666666</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>4.75</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
         <v>2.04</v>
@@ -2370,10 +2370,10 @@
         <v>3.34</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>2.97</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="N12" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.32</v>
+        <v>3.21</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="Q12" t="n">
         <v>3.64</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
         <v>2.57</v>
       </c>
       <c r="T12" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="U12" t="n">
         <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -1891,16 +1891,16 @@
         <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.98</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
         <v>1.2</v>
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.87</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>5.43</v>
       </c>
       <c r="O16" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="P16" t="n">
         <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.84</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
         <v>1.37</v>
@@ -2349,7 +2349,7 @@
         <v>2.81</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>2.33</v>
       </c>
       <c r="U16" t="n">
         <v>1.39</v>
@@ -2370,22 +2370,22 @@
         <v>3.34</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
         <v>2.97</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE16" t="n">
         <v>1.86</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AG16" t="n">
         <v>1.23</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
-        <v>4.51</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
         <v>2.69</v>
       </c>
       <c r="T11" t="n">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z11" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
         <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46037.60416666666</v>
@@ -1968,58 +1968,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>3.33</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
         <v>3.19</v>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
         <v>2.91</v>
       </c>
       <c r="T13" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
         <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
         <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="AD13" t="n">
         <v>1.23</v>
@@ -2028,10 +2028,10 @@
         <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AH13" t="n">
         <v>1.38</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -1745,16 +1745,16 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="T11" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="U11" t="n">
         <v>1.32</v>
@@ -1775,28 +1775,28 @@
         <v>2.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD11" t="n">
         <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46037.60416666666</v>
@@ -2001,13 +2001,13 @@
         <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
         <v>3.15</v>
@@ -2022,7 +2022,7 @@
         <v>3.44</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
         <v>1.8</v>
@@ -2325,43 +2325,43 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="M16" t="n">
-        <v>3.87</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>5.43</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>2.33</v>
+        <v>2.73</v>
       </c>
       <c r="U16" t="n">
         <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
         <v>1.24</v>
@@ -2370,13 +2370,13 @@
         <v>3.34</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AD16" t="n">
         <v>1.31</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1730,28 +1730,28 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q11" t="n">
         <v>2.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>2.67</v>
+        <v>2.53</v>
       </c>
       <c r="T11" t="n">
         <v>3.41</v>
@@ -1760,7 +1760,7 @@
         <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -1772,31 +1772,31 @@
         <v>1.42</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
         <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
         <v>2.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
         <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46037.60416666666</v>
@@ -1849,31 +1849,31 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="O12" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
         <v>2.13</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S12" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="U12" t="n">
         <v>1.34</v>
@@ -1891,19 +1891,19 @@
         <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
         <v>1.86</v>
@@ -1912,7 +1912,7 @@
         <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
         <v>1.53</v>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="M13" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.19</v>
+        <v>3.6</v>
       </c>
       <c r="P13" t="n">
         <v>2.21</v>
@@ -1989,7 +1989,7 @@
         <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="T13" t="n">
         <v>2.8</v>
@@ -1998,7 +1998,7 @@
         <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
@@ -2007,22 +2007,22 @@
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
         <v>3.44</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
         <v>1.8</v>
@@ -2034,7 +2034,7 @@
         <v>1.56</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46037.69791666666</v>
@@ -2355,7 +2355,7 @@
         <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
@@ -2367,7 +2367,7 @@
         <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA16" t="n">
         <v>1.95</v>
@@ -2379,7 +2379,7 @@
         <v>3.04</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
         <v>1.86</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1305,10 +1305,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1662,10 +1662,10 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1739,7 +1739,7 @@
         <v>2.04</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P11" t="n">
         <v>1.93</v>
@@ -1751,16 +1751,16 @@
         <v>1.51</v>
       </c>
       <c r="S11" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
-        <v>3.41</v>
+        <v>3.05</v>
       </c>
       <c r="U11" t="n">
         <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -1784,7 +1784,7 @@
         <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
         <v>2.03</v>
@@ -1858,13 +1858,13 @@
         <v>3.03</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="R12" t="n">
         <v>1.49</v>
@@ -1909,13 +1909,13 @@
         <v>1.86</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46037.6875</v>
@@ -1977,7 +1977,7 @@
         <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P13" t="n">
         <v>2.21</v>
@@ -1989,25 +1989,25 @@
         <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="U13" t="n">
         <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
         <v>3.2</v>
@@ -2031,10 +2031,10 @@
         <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46037.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2334,7 +2334,7 @@
         <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="P16" t="n">
         <v>2.16</v>
@@ -2343,31 +2343,31 @@
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="T16" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
         <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>6.55</v>
+        <v>6.65</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
         <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA16" t="n">
         <v>1.95</v>
@@ -2376,22 +2376,22 @@
         <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46037.71875</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2328,10 +2328,10 @@
         <v>1.53</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="O16" t="n">
         <v>2.16</v>
@@ -2340,13 +2340,13 @@
         <v>2.16</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>5.71</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.81</v>
+        <v>2.98</v>
       </c>
       <c r="T16" t="n">
         <v>2.85</v>
@@ -2361,7 +2361,7 @@
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
         <v>1.24</v>
@@ -2373,22 +2373,22 @@
         <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
         <v>1.97</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
         <v>2.27</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="M7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD7" t="n">
         <v>1.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46037.47916666666</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
         <v>2</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="N11" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
         <v>4.2</v>
@@ -1748,22 +1748,22 @@
         <v>2.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="T11" t="n">
-        <v>3.05</v>
+        <v>3.41</v>
       </c>
       <c r="U11" t="n">
         <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
@@ -1775,28 +1775,28 @@
         <v>2.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB11" t="n">
         <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.3</v>
+        <v>4.35</v>
       </c>
       <c r="AD11" t="n">
         <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
         <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46037.60416666666</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>3.03</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
         <v>3.25</v>
@@ -1873,19 +1873,19 @@
         <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
         <v>1.36</v>
@@ -1894,19 +1894,19 @@
         <v>2.84</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
         <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AF12" t="n">
         <v>1.91</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="N13" t="n">
         <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="P13" t="n">
         <v>2.21</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="R13" t="n">
         <v>1.41</v>
@@ -1992,37 +1992,37 @@
         <v>2.91</v>
       </c>
       <c r="T13" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
         <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
         <v>1.8</v>
@@ -2031,10 +2031,10 @@
         <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46037.69791666666</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="M12" t="n">
         <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
         <v>1.49</v>
@@ -1873,43 +1873,43 @@
         <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>3.37</v>
+        <v>2.88</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="Z12" t="n">
         <v>2.84</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD12" t="n">
         <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG12" t="n">
         <v>1.39</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46037.375</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46037.41666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46037.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46037.41666666666</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46037.42013888889</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="O7" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="P7" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S7" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="U7" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V7" t="n">
-        <v>4.85</v>
+        <v>4.65</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
         <v>1.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46037.47916666666</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.53</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46037.53125</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="AC10" t="n">
         <v>2</v>
@@ -1730,40 +1730,40 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="O11" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="T11" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
         <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.03</v>
@@ -1775,13 +1775,13 @@
         <v>2.95</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
         <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="AD11" t="n">
         <v>1.2</v>
@@ -1793,10 +1793,10 @@
         <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46037.60416666666</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="O12" t="n">
         <v>3.05</v>
@@ -1864,25 +1864,25 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>2.88</v>
+        <v>3.37</v>
       </c>
       <c r="U12" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
@@ -1891,31 +1891,31 @@
         <v>1.41</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>4.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
         <v>1.86</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46037.6875</v>
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="M13" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
         <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="P13" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.21</v>
+        <v>2.93</v>
       </c>
       <c r="R13" t="n">
         <v>1.41</v>
@@ -1998,43 +1998,43 @@
         <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
         <v>3.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE13" t="n">
         <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46037.69791666666</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2328,70 +2328,70 @@
         <v>1.53</v>
       </c>
       <c r="M16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="P16" t="n">
-        <v>2.16</v>
+        <v>2.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.71</v>
+        <v>4.9</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
         <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>6.65</v>
+        <v>6.6</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
         <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA16" t="n">
         <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
         <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46037.71875</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>3.48</v>
       </c>
       <c r="O2" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.95</v>
+        <v>4.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="S2" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="T2" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="U2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V2" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46037.375</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.98</v>
+        <v>2.39</v>
       </c>
       <c r="M3" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>3.23</v>
       </c>
       <c r="O3" t="n">
-        <v>2.72</v>
+        <v>3.26</v>
       </c>
       <c r="P3" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.28</v>
+        <v>4.47</v>
       </c>
       <c r="R3" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="T3" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V3" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46037.41666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>6.45</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>17.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>1.56</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>2.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.79</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.31</v>
       </c>
       <c r="S4" t="n">
-        <v>2.11</v>
+        <v>2.97</v>
       </c>
       <c r="T4" t="n">
-        <v>4.1</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="V4" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="W4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.02</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.68</v>
+        <v>1.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.89</v>
+        <v>1.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.34</v>
+        <v>2.18</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.15</v>
+        <v>2.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.51</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>4.8</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46037.41666666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.15</v>
+        <v>2.13</v>
       </c>
       <c r="M5" t="n">
-        <v>5.4</v>
+        <v>2.83</v>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>3.58</v>
       </c>
       <c r="O5" t="n">
-        <v>1.54</v>
+        <v>2.96</v>
       </c>
       <c r="P5" t="n">
-        <v>2.53</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>4.84</v>
       </c>
       <c r="R5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V5" t="n">
+        <v>13</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG5" t="n">
         <v>1.32</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AH5" t="n">
-        <v>5</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46037.41666666666</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.39</v>
+        <v>1.1</v>
       </c>
       <c r="M3" t="n">
-        <v>2.67</v>
+        <v>6.45</v>
       </c>
       <c r="N3" t="n">
-        <v>3.23</v>
+        <v>17.5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.26</v>
+        <v>1.56</v>
       </c>
       <c r="P3" t="n">
-        <v>1.73</v>
+        <v>2.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.47</v>
+        <v>14</v>
       </c>
       <c r="R3" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>2.08</v>
+        <v>2.97</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="U3" t="n">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="V3" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="W3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.02</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.69</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.12</v>
+        <v>4.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.2</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.32</v>
+        <v>2.18</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.06</v>
+        <v>1.51</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.45</v>
+        <v>4.8</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46037.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V4" t="n">
+        <v>13</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.1</v>
       </c>
-      <c r="M4" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="N4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>14</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.14</v>
+        <v>1.69</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.33</v>
+        <v>2.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.58</v>
+        <v>3.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.18</v>
+        <v>1.32</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.51</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.88</v>
+        <v>2.31</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.8</v>
+        <v>1.45</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46037.41666666666</v>
@@ -1135,34 +1135,34 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="N6" t="n">
-        <v>3.31</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>2.93</v>
+        <v>3.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="T6" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="U6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V6" t="n">
         <v>8</v>
@@ -1174,16 +1174,16 @@
         <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.56</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
         <v>4.5</v>
@@ -1192,16 +1192,16 @@
         <v>1.13</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46037.42013888889</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N7" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8</v>
+        <v>4.29</v>
       </c>
       <c r="P7" t="n">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="Q7" t="n">
         <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="T7" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="V7" t="n">
-        <v>4.65</v>
+        <v>4.95</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.19</v>
+        <v>1.98</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46037.47916666666</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="M8" t="n">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M9" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="N9" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="P9" t="n">
         <v>2.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.53</v>
+        <v>7.42</v>
       </c>
       <c r="R9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="T9" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="U9" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="V9" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46037.53125</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N10" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AC10" t="n">
         <v>2</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
@@ -1745,10 +1745,10 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="S11" t="n">
         <v>2.45</v>
@@ -1760,7 +1760,7 @@
         <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -1769,34 +1769,34 @@
         <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
         <v>4.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AF11" t="n">
         <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46037.60416666666</v>
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
         <v>3.05</v>
@@ -1864,7 +1864,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.28</v>
+        <v>3.55</v>
       </c>
       <c r="R12" t="n">
         <v>1.47</v>
@@ -1873,10 +1873,10 @@
         <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>3.37</v>
+        <v>3.18</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
         <v>8.6</v>
@@ -1894,13 +1894,13 @@
         <v>2.86</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AD12" t="n">
         <v>1.2</v>
@@ -1912,10 +1912,10 @@
         <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46037.6875</v>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
         <v>2.5</v>
@@ -1983,19 +1983,19 @@
         <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.93</v>
+        <v>3.18</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="T13" t="n">
         <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
         <v>7.6</v>
@@ -2007,31 +2007,31 @@
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.42</v>
+        <v>3.12</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.77</v>
       </c>
-      <c r="AC13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF13" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AH13" t="n">
         <v>1.4</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2325,28 +2325,28 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>5.48</v>
       </c>
       <c r="O16" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.43</v>
+        <v>2.17</v>
       </c>
       <c r="Q16" t="n">
         <v>4.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="T16" t="n">
         <v>2.65</v>
@@ -2355,7 +2355,7 @@
         <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
@@ -2367,28 +2367,28 @@
         <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AC16" t="n">
         <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.86</v>
       </c>
-      <c r="AF16" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
         <v>2.2</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="M2" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.48</v>
+        <v>3.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.74</v>
+        <v>4.68</v>
       </c>
       <c r="R2" t="n">
         <v>1.59</v>
@@ -698,19 +698,19 @@
         <v>1.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AD2" t="n">
         <v>1.12</v>
@@ -722,10 +722,10 @@
         <v>1.57</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46037.375</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>6.45</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>17.5</v>
+        <v>3.71</v>
       </c>
       <c r="O3" t="n">
-        <v>1.56</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>5.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>2.97</v>
+        <v>2.09</v>
       </c>
       <c r="T3" t="n">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="V3" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="W3" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.14</v>
+        <v>1.67</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.33</v>
+        <v>2.12</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>3.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.18</v>
+        <v>1.32</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.51</v>
+        <v>1.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.88</v>
+        <v>2.36</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.8</v>
+        <v>1.57</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46037.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.39</v>
+        <v>1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>2.67</v>
+        <v>7.25</v>
       </c>
       <c r="N4" t="n">
-        <v>3.23</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>3.26</v>
+        <v>1.56</v>
       </c>
       <c r="P4" t="n">
-        <v>1.73</v>
+        <v>2.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.47</v>
+        <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>2.08</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.17</v>
       </c>
-      <c r="V4" t="n">
-        <v>13</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.69</v>
-      </c>
       <c r="Z4" t="n">
-        <v>2.12</v>
+        <v>4.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.2</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.32</v>
+        <v>2.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.4</v>
+        <v>2.26</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.31</v>
+        <v>2.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.45</v>
+        <v>4.8</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46037.41666666666</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.96</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.84</v>
+        <v>4.25</v>
       </c>
       <c r="R5" t="n">
         <v>1.63</v>
@@ -1040,10 +1040,10 @@
         <v>2.11</v>
       </c>
       <c r="T5" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
         <v>13</v>
@@ -1067,16 +1067,16 @@
         <v>1.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="AD5" t="n">
         <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG5" t="n">
         <v>1.32</v>
@@ -1849,28 +1849,28 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
         <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>2.69</v>
       </c>
       <c r="T12" t="n">
         <v>3.18</v>
@@ -1879,7 +1879,7 @@
         <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
@@ -1888,28 +1888,28 @@
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.86</v>
+        <v>3.01</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
         <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
         <v>1.39</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.18</v>
+        <v>3.95</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>1.15</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6</v>
+        <v>7.25</v>
       </c>
       <c r="N3" t="n">
-        <v>3.71</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
-        <v>2.95</v>
+        <v>1.56</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>2.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.01</v>
+        <v>14.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>2.09</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="U3" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.17</v>
       </c>
-      <c r="V3" t="n">
-        <v>13</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.67</v>
-      </c>
       <c r="Z3" t="n">
-        <v>2.12</v>
+        <v>4.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.07</v>
+        <v>1.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.32</v>
+        <v>2.27</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.4</v>
+        <v>2.26</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.57</v>
+        <v>4.8</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46037.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.15</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>7.25</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>3.71</v>
       </c>
       <c r="O4" t="n">
-        <v>1.56</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>2.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.2</v>
+        <v>5.01</v>
       </c>
       <c r="R4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V4" t="n">
+        <v>13</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.32</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2.27</v>
-      </c>
       <c r="AC4" t="n">
-        <v>2.26</v>
+        <v>5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.8</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46037.41666666666</v>
@@ -1730,31 +1730,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="R11" t="n">
         <v>1.52</v>
       </c>
       <c r="S11" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="U11" t="n">
         <v>1.32</v>
@@ -1766,34 +1766,34 @@
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
         <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.94</v>
+        <v>2.77</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
         <v>1.93</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AH11" t="n">
         <v>1.32</v>
@@ -1968,10 +1968,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="M13" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
         <v>2.5</v>
@@ -1980,25 +1980,25 @@
         <v>3.63</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
         <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>2.59</v>
+        <v>2.91</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
@@ -2007,10 +2007,10 @@
         <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="AA13" t="n">
         <v>2.14</v>
@@ -2025,7 +2025,7 @@
         <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
         <v>1.96</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.15</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>7.25</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>3.71</v>
       </c>
       <c r="O3" t="n">
-        <v>1.56</v>
+        <v>2.95</v>
       </c>
       <c r="P3" t="n">
-        <v>2.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.2</v>
+        <v>5.01</v>
       </c>
       <c r="R3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V3" t="n">
+        <v>13</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.32</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.27</v>
-      </c>
       <c r="AC3" t="n">
-        <v>2.26</v>
+        <v>5.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>4.8</v>
+        <v>1.57</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46037.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6</v>
+        <v>7.25</v>
       </c>
       <c r="N4" t="n">
-        <v>3.71</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>1.56</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>2.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.01</v>
+        <v>14.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>2.09</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y4" t="n">
         <v>1.17</v>
       </c>
-      <c r="V4" t="n">
-        <v>13</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.67</v>
-      </c>
       <c r="Z4" t="n">
-        <v>2.12</v>
+        <v>4.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.07</v>
+        <v>1.55</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.32</v>
+        <v>2.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.4</v>
+        <v>2.26</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>4.8</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46037.41666666666</v>
@@ -2093,7 +2093,7 @@
         <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="M16" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>5.48</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.37</v>
@@ -2349,7 +2349,7 @@
         <v>2.81</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="U16" t="n">
         <v>1.39</v>
@@ -2367,13 +2367,13 @@
         <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>2.7</v>
@@ -2388,10 +2388,10 @@
         <v>1.86</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46037.71875</v>
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.95</v>
+        <v>2.96</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>2.33</v>
       </c>
       <c r="N17" t="n">
-        <v>1.83</v>
+        <v>2.93</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -677,19 +677,19 @@
         <v>4.68</v>
       </c>
       <c r="R2" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
         <v>2.18</v>
       </c>
       <c r="T2" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="U2" t="n">
         <v>1.2</v>
       </c>
       <c r="V2" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
@@ -713,7 +713,7 @@
         <v>5.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE2" t="n">
         <v>2.2</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>18</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>21</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC3" t="n">
         <v>2.2</v>
       </c>
-      <c r="M3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="O3" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="AD3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.17</v>
       </c>
-      <c r="V3" t="n">
-        <v>13</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AG3" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.57</v>
+        <v>6.5</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46037.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.15</v>
+        <v>2.15</v>
       </c>
       <c r="M4" t="n">
-        <v>7.25</v>
+        <v>2.62</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.56</v>
+        <v>2.93</v>
       </c>
       <c r="P4" t="n">
-        <v>2.84</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.2</v>
+        <v>4.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.34</v>
+        <v>3.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>1.63</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.75</v>
+        <v>2.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.26</v>
+        <v>5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.8</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46037.41666666666</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="P5" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S5" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="T5" t="n">
         <v>3.9</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
         <v>13</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.2</v>
+        <v>5.95</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
         <v>1.32</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46037.41666666666</v>
@@ -1135,28 +1135,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="M6" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.15</v>
+        <v>3.31</v>
       </c>
       <c r="O6" t="n">
         <v>3.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.08</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S6" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="T6" t="n">
         <v>3.42</v>
@@ -1171,31 +1171,31 @@
         <v>1.05</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
         <v>1.3</v>
@@ -1254,70 +1254,70 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="O7" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="U7" t="n">
         <v>1.56</v>
       </c>
       <c r="V7" t="n">
-        <v>4.95</v>
+        <v>5.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="n">
         <v>1.21</v>
@@ -1376,10 +1376,10 @@
         <v>1.72</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>4.13</v>
+        <v>4.33</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1492,37 +1492,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="N9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q9" t="n">
         <v>9</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>7.42</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
         <v>2.91</v>
       </c>
       <c r="T9" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V9" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
@@ -1534,31 +1534,31 @@
         <v>1.19</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG9" t="n">
         <v>1.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46037.53125</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AC10" t="n">
         <v>2</v>
@@ -1730,43 +1730,43 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.56</v>
+        <v>3.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="R11" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>3.34</v>
+        <v>3.41</v>
       </c>
       <c r="U11" t="n">
         <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
         <v>1.38</v>
@@ -1775,22 +1775,22 @@
         <v>2.77</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
         <v>1.39</v>
@@ -1849,64 +1849,64 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.66</v>
+        <v>2.38</v>
       </c>
       <c r="M12" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
         <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>2.69</v>
+        <v>2.56</v>
       </c>
       <c r="T12" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.01</v>
+        <v>2.86</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
         <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AF12" t="n">
         <v>1.85</v>
@@ -1915,7 +1915,7 @@
         <v>1.39</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46037.6875</v>
@@ -1968,70 +1968,70 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
         <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.63</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
         <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="T13" t="n">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="U13" t="n">
         <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y13" t="n">
         <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
         <v>1.4</v>
@@ -2334,7 +2334,7 @@
         <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="P16" t="n">
         <v>2.14</v>
@@ -2376,22 +2376,22 @@
         <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>3.35</v>
       </c>
       <c r="AD16" t="n">
         <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46037.71875</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>3.85</v>
       </c>
       <c r="O3" t="n">
-        <v>1.35</v>
+        <v>2.88</v>
       </c>
       <c r="P3" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>21</v>
+        <v>4.8</v>
       </c>
       <c r="R3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V3" t="n">
+        <v>13</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.32</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AH3" t="n">
-        <v>6.5</v>
+        <v>1.62</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46037.41666666666</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.15</v>
+        <v>1.15</v>
       </c>
       <c r="M4" t="n">
-        <v>2.62</v>
+        <v>5.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>18</v>
       </c>
       <c r="O4" t="n">
-        <v>2.93</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>2.65</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.75</v>
+        <v>21</v>
       </c>
       <c r="R4" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>3.8</v>
+        <v>2.17</v>
       </c>
       <c r="U4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.17</v>
       </c>
-      <c r="V4" t="n">
-        <v>10</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>1.02</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.11</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.63</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.12</v>
+        <v>4.35</v>
       </c>
       <c r="AA4" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.36</v>
+        <v>4.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.5</v>
+        <v>1.17</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.57</v>
+        <v>6.5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46037.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,61 +1016,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="O5" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="S5" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="T5" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U5" t="n">
         <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.95</v>
+        <v>5.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
         <v>2.36</v>
@@ -1079,10 +1079,10 @@
         <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46037.41666666666</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="O3" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="S3" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="T3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.95</v>
+        <v>5.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46037.41666666666</v>
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="O4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>3.12</v>
       </c>
       <c r="T4" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="U4" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="V4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="W4" t="n">
         <v>1.17</v>
@@ -936,34 +936,34 @@
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.35</v>
+        <v>5.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE4" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46037.41666666666</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.68</v>
+        <v>3.3</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.04</v>
+        <v>2.23</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
@@ -1745,22 +1745,22 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="T11" t="n">
-        <v>3.41</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
         <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
@@ -1775,25 +1775,25 @@
         <v>2.77</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AC11" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AF11" t="n">
         <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="n">
         <v>1.32</v>
@@ -1968,19 +1968,19 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O13" t="n">
         <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
         <v>3.05</v>
@@ -1989,52 +1989,52 @@
         <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
         <v>2.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46037.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46037.70833333334</v>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>2.04</v>
+        <v>4.45</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.8</v>
+        <v>2.63</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="T16" t="n">
-        <v>2.73</v>
+        <v>3.04</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46037.71875</v>
+        <v>46037.70833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,76 +2444,76 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.96</v>
+        <v>1.53</v>
       </c>
       <c r="M17" t="n">
-        <v>2.33</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>2.93</v>
+        <v>5.3</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>46037.79166666666</v>
+        <v>46037.71875</v>
       </c>
     </row>
     <row r="18">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2563,76 +2563,76 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z18" t="n">
         <v>3.05</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
       <c r="AA18" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>46037.89583333334</v>
+        <v>46037.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -655,32 +655,32 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.92</v>
+        <v>2.37</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="N2" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.68</v>
+        <v>4.63</v>
       </c>
       <c r="R2" t="n">
         <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="T2" t="n">
         <v>3.6</v>
@@ -695,25 +695,25 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE2" t="n">
         <v>2.2</v>
@@ -722,10 +722,10 @@
         <v>1.57</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46037.375</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.85</v>
+        <v>1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>2.9</v>
+        <v>10</v>
       </c>
       <c r="N3" t="n">
-        <v>4.15</v>
+        <v>41</v>
       </c>
       <c r="O3" t="n">
-        <v>2.78</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>2.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.25</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2</v>
+        <v>3.12</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>1.64</v>
       </c>
       <c r="V3" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.11</v>
       </c>
-      <c r="Y3" t="n">
-        <v>1.62</v>
-      </c>
       <c r="Z3" t="n">
-        <v>2.23</v>
+        <v>5.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.75</v>
+        <v>1.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.55</v>
+        <v>2.15</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.34</v>
+        <v>3.85</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.76</v>
+        <v>6.7</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46037.41666666666</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
-        <v>41</v>
+        <v>4.15</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>2.78</v>
       </c>
       <c r="P4" t="n">
-        <v>2.76</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>19</v>
+        <v>5.25</v>
       </c>
       <c r="R4" t="n">
-        <v>1.28</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>3.12</v>
+        <v>2.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.96</v>
+        <v>3.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.64</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.11</v>
+        <v>1.62</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.3</v>
+        <v>2.23</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.45</v>
+        <v>2.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.15</v>
+        <v>5.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.65</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>3.85</v>
+        <v>2.34</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AH4" t="n">
-        <v>6.7</v>
+        <v>1.76</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46037.41666666666</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="M5" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="O5" t="n">
         <v>2.93</v>
@@ -1064,7 +1064,7 @@
         <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AC5" t="n">
         <v>5.4</v>
@@ -1135,16 +1135,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>3.31</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="P6" t="n">
         <v>1.95</v>
@@ -1153,55 +1153,55 @@
         <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S6" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="T6" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V6" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y6" t="n">
         <v>1.43</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AD6" t="n">
         <v>1.12</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46037.42013888889</v>
@@ -1266,37 +1266,37 @@
         <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="Q7" t="n">
         <v>2.38</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="U7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AA7" t="n">
         <v>1.47</v>
@@ -1382,64 +1382,64 @@
         <v>4.33</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB8" t="n">
         <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46037.52083333334</v>
@@ -1501,28 +1501,28 @@
         <v>7.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="P9" t="n">
         <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
         <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="W9" t="n">
         <v>1.08</v>
@@ -1531,10 +1531,10 @@
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="AA9" t="n">
         <v>1.55</v>
@@ -1543,22 +1543,22 @@
         <v>2.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AG9" t="n">
         <v>1.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46037.53125</v>
@@ -1620,40 +1620,40 @@
         <v>2.12</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA10" t="n">
         <v>1.37</v>
@@ -1668,16 +1668,16 @@
         <v>1.72</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46037.5625</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
@@ -1775,10 +1775,10 @@
         <v>2.77</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
         <v>4.05</v>
@@ -1861,37 +1861,37 @@
         <v>3.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T12" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V12" t="n">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="AA12" t="n">
         <v>2.1</v>
@@ -1903,16 +1903,16 @@
         <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
         <v>1.5</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="M13" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
         <v>3.3</v>
@@ -2013,10 +2013,10 @@
         <v>3.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC13" t="n">
         <v>4</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46037.70833333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.3</v>
+        <v>1.22</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="N15" t="n">
-        <v>2.1</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46037.70833333334</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="O16" t="n">
-        <v>4.45</v>
+        <v>4.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z16" t="n">
         <v>3.04</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.92</v>
-      </c>
       <c r="AA16" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.72</v>
+        <v>3.28</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46037.70833333334</v>
@@ -2453,40 +2453,40 @@
         <v>5.3</v>
       </c>
       <c r="O17" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
         <v>4.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>2.81</v>
+        <v>2.98</v>
       </c>
       <c r="T17" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="AA17" t="n">
         <v>1.95</v>
@@ -2501,16 +2501,16 @@
         <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG17" t="n">
         <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46037.71875</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="O18" t="n">
         <v>4.05</v>
@@ -2608,10 +2608,10 @@
         <v>3.05</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>3.42</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -761,20 +761,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1379,16 +1379,16 @@
         <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="P8" t="n">
         <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.99</v>
+        <v>4.82</v>
       </c>
       <c r="R8" t="n">
         <v>1.41</v>
@@ -1397,7 +1397,7 @@
         <v>2.56</v>
       </c>
       <c r="T8" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="U8" t="n">
         <v>1.32</v>
@@ -1412,34 +1412,34 @@
         <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD8" t="n">
         <v>1.22</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AG8" t="n">
         <v>1.24</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46037.52083333334</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M9" t="n">
-        <v>5.1</v>
+        <v>4.85</v>
       </c>
       <c r="N9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="T9" t="n">
         <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="V9" t="n">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.64</v>
+        <v>1.77</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46037.53125</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.5</v>
+        <v>1.22</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="N14" t="n">
+        <v>11</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.95</v>
       </c>
-      <c r="O14" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC14" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46037.70833333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.22</v>
-      </c>
-      <c r="M15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N15" t="n">
-        <v>11</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46037.70833333334</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -1240,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1475,20 +1475,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N10" t="n">
         <v>2.7</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S10" t="n">
         <v>3.7</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.16</v>
       </c>
-      <c r="S10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V10" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Z10" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>3.11</v>
+        <v>2.75</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46037.5625</v>
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.68</v>
+        <v>3.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="N11" t="n">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.93</v>
+        <v>2.96</v>
       </c>
       <c r="R11" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="T11" t="n">
         <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V11" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="W11" t="n">
         <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AF11" t="n">
         <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46037.60416666666</v>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="O12" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P12" t="n">
         <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="R12" t="n">
         <v>1.48</v>
@@ -1873,19 +1873,19 @@
         <v>2.53</v>
       </c>
       <c r="T12" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="U12" t="n">
         <v>1.31</v>
       </c>
       <c r="V12" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
         <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
         <v>1.37</v>
@@ -1894,28 +1894,28 @@
         <v>2.82</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
         <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46037.6875</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.84</v>
+        <v>3.06</v>
       </c>
       <c r="M13" t="n">
         <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="O13" t="n">
         <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="R13" t="n">
         <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
         <v>2.8</v>
@@ -1998,43 +1998,43 @@
         <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="W13" t="n">
         <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46037.69791666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.22</v>
       </c>
-      <c r="M14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N14" t="n">
-        <v>11</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46037.70833333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.5</v>
+        <v>1.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.95</v>
+        <v>9.75</v>
       </c>
       <c r="O15" t="n">
-        <v>4.45</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.63</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.56</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>2.35</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="V15" t="n">
-        <v>7.6</v>
+        <v>5.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.92</v>
+        <v>3.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.72</v>
+        <v>2.75</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.22</v>
+        <v>3.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46037.70833333334</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.08</v>
-      </c>
-      <c r="O16" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.18</v>
       </c>
       <c r="AB16" t="n">
         <v>1.61</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46037.70833333334</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="O18" t="n">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="P18" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="T18" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="W18" t="n">
         <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.95</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46037.875</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -1594,20 +1594,20 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1713,20 +1713,20 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.15</v>
+        <v>3.3</v>
       </c>
       <c r="M15" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>9.75</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>2.57</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="U15" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>5.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE15" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.6</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46037.70833333334</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.3</v>
+        <v>1.15</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>9.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>1.62</v>
       </c>
       <c r="P16" t="n">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.57</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="V16" t="n">
-        <v>8.699999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
         <v>1.04</v>
       </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.33</v>
+        <v>3.6</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46037.70833333334</v>
@@ -2444,37 +2444,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
         <v>4.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98</v>
+        <v>2.66</v>
       </c>
       <c r="T17" t="n">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="W17" t="n">
         <v>1.04</v>
@@ -2483,13 +2483,13 @@
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB17" t="n">
         <v>1.75</v>
@@ -2498,19 +2498,19 @@
         <v>3.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46037.71875</v>

--- a/jogos_2026-01-15.xlsx
+++ b/jogos_2026-01-15.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>4.15</v>
+        <v>3.73</v>
       </c>
       <c r="O4" t="n">
-        <v>2.78</v>
+        <v>2.93</v>
       </c>
       <c r="P4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.25</v>
+        <v>4.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T4" t="n">
         <v>3.8</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
         <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.14</v>
+        <v>1.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46037.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="N5" t="n">
-        <v>3.73</v>
+        <v>4.15</v>
       </c>
       <c r="O5" t="n">
-        <v>2.93</v>
+        <v>2.78</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="R5" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
         <v>3.8</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1.11</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AA5" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46037.41666666666</v>
@@ -1832,20 +1832,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -1951,20 +1951,20 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2180,16 +2180,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2202,77 +2202,77 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.3</v>
+        <v>1.15</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>9.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>1.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.07</v>
+        <v>2.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.57</v>
+        <v>10</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>5.4</v>
       </c>
       <c r="W15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.04</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>3.6</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46037.70833333334</v>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.15</v>
+        <v>3.3</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>9.75</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.45</v>
+        <v>2.07</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>2.57</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>2.35</v>
+        <v>2.97</v>
       </c>
       <c r="U16" t="n">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="V16" t="n">
-        <v>5.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE16" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.6</v>
+        <v>1.33</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46037.70833333334</v>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2563,61 +2563,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="O18" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
       <c r="T18" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
         <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE18" t="n">
         <v>1.73</v>
@@ -2629,7 +2629,7 @@
         <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46037.875</v>
